--- a/assets/libreoffice_calc_njc/b8185158-1fda-4729-ad1a-b76a8afa9ecf/Finance_Sheet2_Sum.xlsx
+++ b/assets/libreoffice_calc_njc/b8185158-1fda-4729-ad1a-b76a8afa9ecf/Finance_Sheet2_Sum.xlsx
@@ -114,8 +114,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -137,24 +141,22 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9.14453125" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <f aca="false">SUM(Sheet1!A2:A100)</f>
-        <v>14147</v>
-      </c>
-      <c r="B2" s="0" t="n">
-        <f aca="false">SUM(Sheet1!B2:B100)</f>
+      <c r="A2" s="1" t="n">
         <v>11150000</v>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>8420000</v>
       </c>
     </row>
   </sheetData>
@@ -174,117 +176,117 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>2018</v>
       </c>
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>1250000</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>980000</v>
       </c>
-      <c r="D2" s="0" t="n">
+      <c r="D2" s="1" t="n">
         <v>270000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
+      <c r="A3" s="1" t="n">
         <v>2019</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>1380000</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>1050000</v>
       </c>
-      <c r="D3" s="0" t="n">
+      <c r="D3" s="1" t="n">
         <v>330000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
+      <c r="A4" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>1210000</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>940000</v>
       </c>
-      <c r="D4" s="0" t="n">
+      <c r="D4" s="1" t="n">
         <v>270000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="B5" s="0" t="n">
+      <c r="B5" s="1" t="n">
         <v>1520000</v>
       </c>
-      <c r="C5" s="0" t="n">
+      <c r="C5" s="1" t="n">
         <v>1150000</v>
       </c>
-      <c r="D5" s="0" t="n">
+      <c r="D5" s="1" t="n">
         <v>370000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
+      <c r="A6" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="B6" s="0" t="n">
+      <c r="B6" s="1" t="n">
         <v>1750000</v>
       </c>
-      <c r="C6" s="0" t="n">
+      <c r="C6" s="1" t="n">
         <v>1310000</v>
       </c>
-      <c r="D6" s="0" t="n">
+      <c r="D6" s="1" t="n">
         <v>440000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="B7" s="0" t="n">
+      <c r="B7" s="1" t="n">
         <v>1940000</v>
       </c>
-      <c r="C7" s="0" t="n">
+      <c r="C7" s="1" t="n">
         <v>1440000</v>
       </c>
-      <c r="D7" s="0" t="n">
+      <c r="D7" s="1" t="n">
         <v>500000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="B8" s="0" t="n">
+      <c r="B8" s="1" t="n">
         <v>2100000</v>
       </c>
-      <c r="C8" s="0" t="n">
+      <c r="C8" s="1" t="n">
         <v>1550000</v>
       </c>
-      <c r="D8" s="0" t="n">
+      <c r="D8" s="1" t="n">
         <v>550000</v>
       </c>
     </row>

--- a/assets/libreoffice_calc_njc/b8185158-1fda-4729-ad1a-b76a8afa9ecf/Finance_Sheet2_Sum.xlsx
+++ b/assets/libreoffice_calc_njc/b8185158-1fda-4729-ad1a-b76a8afa9ecf/Finance_Sheet2_Sum.xlsx
@@ -141,7 +141,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9.15234375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -151,11 +151,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
+        <f aca="false">SUM(Sheet1!B2:B8)</f>
         <v>11150000</v>
       </c>
       <c r="B2" s="1" t="n">
+        <f aca="false">SUM(Sheet1!C2:C8)</f>
         <v>8420000</v>
       </c>
     </row>

--- a/assets/libreoffice_calc_njc/b8185158-1fda-4729-ad1a-b76a8afa9ecf/Finance_Sheet2_Sum.xlsx
+++ b/assets/libreoffice_calc_njc/b8185158-1fda-4729-ad1a-b76a8afa9ecf/Finance_Sheet2_Sum.xlsx
@@ -48,7 +48,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -70,6 +70,14 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -114,9 +122,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -141,9 +153,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="9.1640625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -181,114 +193,114 @@
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>2018</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>1250000</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>980000</v>
       </c>
-      <c r="D2" s="1" t="n">
+      <c r="D2" s="2" t="n">
         <v>270000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>2019</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>1380000</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>1050000</v>
       </c>
-      <c r="D3" s="1" t="n">
+      <c r="D3" s="2" t="n">
         <v>330000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>2020</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>1210000</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>940000</v>
       </c>
-      <c r="D4" s="1" t="n">
+      <c r="D4" s="2" t="n">
         <v>270000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>2021</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>1520000</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>1150000</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="2" t="n">
         <v>370000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>2022</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>1750000</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>1310000</v>
       </c>
-      <c r="D6" s="1" t="n">
+      <c r="D6" s="2" t="n">
         <v>440000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>2023</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>1940000</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>1440000</v>
       </c>
-      <c r="D7" s="1" t="n">
+      <c r="D7" s="2" t="n">
         <v>500000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>2024</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>2100000</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>1550000</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="2" t="n">
         <v>550000</v>
       </c>
     </row>

--- a/assets/libreoffice_calc_njc/b8185158-1fda-4729-ad1a-b76a8afa9ecf/Finance_Sheet2_Sum.xlsx
+++ b/assets/libreoffice_calc_njc/b8185158-1fda-4729-ad1a-b76a8afa9ecf/Finance_Sheet2_Sum.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t xml:space="preserve">Total Revenue ($)</t>
   </si>
@@ -39,16 +39,20 @@
   </si>
   <si>
     <t xml:space="preserve">Net Income ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total Expense=SUM(C2:C8)s ($)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="General"/>
+    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -71,14 +75,6 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -122,16 +118,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -152,10 +152,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B2"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultColWidth="9.171875" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -165,12 +165,16 @@
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
+        <f aca="false">SUM(Sheet1!C2:C8)</f>
+        <v>8420000</v>
+      </c>
+      <c r="B2" s="2" t="n">
         <f aca="false">SUM(Sheet1!B2:B8)</f>
         <v>11150000</v>
       </c>
-      <c r="B2" s="1" t="n">
-        <f aca="false">SUM(Sheet1!C2:C8)</f>
-        <v>8420000</v>
+      <c r="C2" s="3" t="n">
+        <f aca="false">SUM(Sheet1!C:C)</f>
+        <v>16840000</v>
       </c>
     </row>
   </sheetData>
@@ -189,119 +193,137 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr defaultColWidth="8.54296875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
+      <c r="A2" s="1" t="n">
         <v>2018</v>
       </c>
-      <c r="B2" s="2" t="n">
+      <c r="B2" s="1" t="n">
         <v>1250000</v>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" s="1" t="n">
         <v>980000</v>
       </c>
-      <c r="D2" s="2" t="n">
+      <c r="D2" s="1" t="n">
         <v>270000</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="1" t="n">
         <v>2019</v>
       </c>
-      <c r="B3" s="2" t="n">
+      <c r="B3" s="1" t="n">
         <v>1380000</v>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" s="1" t="n">
         <v>1050000</v>
       </c>
-      <c r="D3" s="2" t="n">
+      <c r="D3" s="1" t="n">
         <v>330000</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="2" t="n">
+      <c r="A4" s="1" t="n">
         <v>2020</v>
       </c>
-      <c r="B4" s="2" t="n">
+      <c r="B4" s="1" t="n">
         <v>1210000</v>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" s="1" t="n">
         <v>940000</v>
       </c>
-      <c r="D4" s="2" t="n">
+      <c r="D4" s="1" t="n">
         <v>270000</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="n">
+      <c r="A5" s="1" t="n">
         <v>2021</v>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B5" s="1" t="n">
         <v>1520000</v>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" s="1" t="n">
         <v>1150000</v>
       </c>
-      <c r="D5" s="2" t="n">
+      <c r="D5" s="1" t="n">
         <v>370000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="n">
+      <c r="A6" s="1" t="n">
         <v>2022</v>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B6" s="1" t="n">
         <v>1750000</v>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" s="1" t="n">
         <v>1310000</v>
       </c>
-      <c r="D6" s="2" t="n">
+      <c r="D6" s="1" t="n">
         <v>440000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="2" t="n">
+      <c r="A7" s="1" t="n">
         <v>2023</v>
       </c>
-      <c r="B7" s="2" t="n">
+      <c r="B7" s="1" t="n">
         <v>1940000</v>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" s="1" t="n">
         <v>1440000</v>
       </c>
-      <c r="D7" s="2" t="n">
+      <c r="D7" s="1" t="n">
         <v>500000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="n">
+      <c r="A8" s="1" t="n">
         <v>2024</v>
       </c>
-      <c r="B8" s="2" t="n">
+      <c r="B8" s="1" t="n">
         <v>2100000</v>
       </c>
-      <c r="C8" s="2" t="n">
+      <c r="C8" s="1" t="n">
         <v>1550000</v>
       </c>
-      <c r="D8" s="2" t="n">
+      <c r="D8" s="1" t="n">
         <v>550000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B9" s="1" t="n">
+        <f aca="false">SUM(B2:B8)</f>
+        <v>11150000</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <f aca="false">SUM(C2:C8)</f>
+        <v>8420000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
